--- a/Короткие названия.xlsx
+++ b/Короткие названия.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\98rog\PycharmProjects\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD013E06-63E7-4640-B896-3568AD621415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F83AE4-5FAF-4CC5-A9B5-471F3779CF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{C75C0F7F-FE97-4E9D-8E7A-FB1708BCE888}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
   <si>
     <t>Итоги 2024 года</t>
   </si>
@@ -963,6 +963,12 @@
   </si>
   <si>
     <t>Короткое название</t>
+  </si>
+  <si>
+    <t>«Медведь» 5 сезон: финальная глава для героев кулинарной трагикомедии</t>
+  </si>
+  <si>
+    <t>Медведь s05</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7C6AF9-5F0C-4EB9-8185-62F3B09665F4}">
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.42578125" customWidth="1"/>
@@ -1376,7 +1382,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1384,7 +1390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="396" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1392,7 +1398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1408,7 +1414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="346.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1416,7 +1422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1424,7 +1430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="396" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="379.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="379.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1464,7 +1470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1472,7 +1478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1480,7 +1486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
@@ -1488,7 +1494,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -1504,7 +1510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -1512,7 +1518,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
@@ -1544,7 +1550,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
@@ -1552,7 +1558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -1560,7 +1566,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
@@ -1568,7 +1574,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>50</v>
       </c>
@@ -1584,7 +1590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>52</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="379.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
@@ -1600,7 +1606,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="346.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>56</v>
       </c>
@@ -1608,7 +1614,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
@@ -1616,7 +1622,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>60</v>
       </c>
@@ -1624,7 +1630,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>64</v>
       </c>
@@ -1640,7 +1646,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>66</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="379.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
@@ -1656,7 +1662,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
@@ -1664,7 +1670,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
@@ -1672,7 +1678,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>74</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>76</v>
       </c>
@@ -1688,7 +1694,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>78</v>
       </c>
@@ -1696,7 +1702,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>80</v>
       </c>
@@ -1704,7 +1710,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>82</v>
       </c>
@@ -1712,7 +1718,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>84</v>
       </c>
@@ -1720,7 +1726,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>86</v>
       </c>
@@ -1728,7 +1734,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>88</v>
       </c>
@@ -1736,7 +1742,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>90</v>
       </c>
@@ -1744,7 +1750,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>92</v>
       </c>
@@ -1752,7 +1758,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>94</v>
       </c>
@@ -1760,7 +1766,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>96</v>
       </c>
@@ -1768,7 +1774,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>98</v>
       </c>
@@ -1776,7 +1782,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>100</v>
       </c>
@@ -1784,7 +1790,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>102</v>
       </c>
@@ -1792,7 +1798,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="346.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>104</v>
       </c>
@@ -1800,7 +1806,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>106</v>
       </c>
@@ -1808,7 +1814,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>108</v>
       </c>
@@ -1816,7 +1822,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>110</v>
       </c>
@@ -1824,7 +1830,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>112</v>
       </c>
@@ -1832,7 +1838,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>114</v>
       </c>
@@ -1840,7 +1846,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>116</v>
       </c>
@@ -1848,7 +1854,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>118</v>
       </c>
@@ -1856,7 +1862,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="346.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>120</v>
       </c>
@@ -1864,7 +1870,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>122</v>
       </c>
@@ -1872,7 +1878,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>124</v>
       </c>
@@ -1880,7 +1886,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>126</v>
       </c>
@@ -1888,7 +1894,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>128</v>
       </c>
@@ -1896,7 +1902,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>130</v>
       </c>
@@ -1904,7 +1910,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>132</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>134</v>
       </c>
@@ -1920,7 +1926,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>136</v>
       </c>
@@ -1928,7 +1934,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>138</v>
       </c>
@@ -1936,7 +1942,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>140</v>
       </c>
@@ -1944,7 +1950,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>142</v>
       </c>
@@ -1952,7 +1958,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>144</v>
       </c>
@@ -1960,7 +1966,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>146</v>
       </c>
@@ -1968,7 +1974,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>148</v>
       </c>
@@ -1976,7 +1982,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>150</v>
       </c>
@@ -1984,7 +1990,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>152</v>
       </c>
@@ -1992,7 +1998,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>154</v>
       </c>
@@ -2000,7 +2006,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>156</v>
       </c>
@@ -2008,7 +2014,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>158</v>
       </c>
@@ -2016,7 +2022,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>160</v>
       </c>
@@ -2024,7 +2030,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>162</v>
       </c>
@@ -2032,7 +2038,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>164</v>
       </c>
@@ -2040,7 +2046,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>166</v>
       </c>
@@ -2048,7 +2054,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>168</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>170</v>
       </c>
@@ -2064,7 +2070,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>172</v>
       </c>
@@ -2072,7 +2078,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>174</v>
       </c>
@@ -2080,7 +2086,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>176</v>
       </c>
@@ -2088,7 +2094,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>178</v>
       </c>
@@ -2096,7 +2102,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="181.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>180</v>
       </c>
@@ -2104,7 +2110,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>182</v>
       </c>
@@ -2112,7 +2118,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>184</v>
       </c>
@@ -2120,7 +2126,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>186</v>
       </c>
@@ -2128,7 +2134,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>188</v>
       </c>
@@ -2136,7 +2142,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>190</v>
       </c>
@@ -2144,7 +2150,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>192</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>194</v>
       </c>
@@ -2160,7 +2166,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>196</v>
       </c>
@@ -2168,7 +2174,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>198</v>
       </c>
@@ -2176,7 +2182,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>200</v>
       </c>
@@ -2184,7 +2190,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>202</v>
       </c>
@@ -2192,7 +2198,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>204</v>
       </c>
@@ -2200,7 +2206,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>206</v>
       </c>
@@ -2208,7 +2214,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>208</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
@@ -2224,7 +2230,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>212</v>
       </c>
@@ -2232,7 +2238,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>214</v>
       </c>
@@ -2240,7 +2246,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>216</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>218</v>
       </c>
@@ -2256,7 +2262,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>220</v>
       </c>
@@ -2264,7 +2270,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>222</v>
       </c>
@@ -2272,7 +2278,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>224</v>
       </c>
@@ -2280,7 +2286,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>226</v>
       </c>
@@ -2288,7 +2294,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>228</v>
       </c>
@@ -2296,7 +2302,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>230</v>
       </c>
@@ -2304,7 +2310,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>232</v>
       </c>
@@ -2312,7 +2318,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>234</v>
       </c>
@@ -2320,7 +2326,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>236</v>
       </c>
@@ -2328,7 +2334,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>238</v>
       </c>
@@ -2336,7 +2342,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>240</v>
       </c>
@@ -2344,7 +2350,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>242</v>
       </c>
@@ -2352,7 +2358,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="396" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>244</v>
       </c>
@@ -2360,7 +2366,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -2368,7 +2374,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>248</v>
       </c>
@@ -2376,7 +2382,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>250</v>
       </c>
@@ -2384,7 +2390,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>252</v>
       </c>
@@ -2392,7 +2398,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>254</v>
       </c>
@@ -2400,7 +2406,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>256</v>
       </c>
@@ -2408,7 +2414,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>258</v>
       </c>
@@ -2416,7 +2422,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>260</v>
       </c>
@@ -2424,7 +2430,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>262</v>
       </c>
@@ -2432,7 +2438,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>264</v>
       </c>
@@ -2440,7 +2446,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>266</v>
       </c>
@@ -2448,7 +2454,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>268</v>
       </c>
@@ -2456,7 +2462,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>270</v>
       </c>
@@ -2464,7 +2470,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>272</v>
       </c>
@@ -2472,7 +2478,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>274</v>
       </c>
@@ -2480,7 +2486,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>276</v>
       </c>
@@ -2488,7 +2494,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>278</v>
       </c>
@@ -2496,7 +2502,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>280</v>
       </c>
@@ -2504,7 +2510,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="231" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>282</v>
       </c>
@@ -2512,7 +2518,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>284</v>
       </c>
@@ -2520,7 +2526,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>286</v>
       </c>
@@ -2528,7 +2534,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>288</v>
       </c>
@@ -2536,7 +2542,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>290</v>
       </c>
@@ -2544,7 +2550,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>292</v>
       </c>
@@ -2552,7 +2558,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="264" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>294</v>
       </c>
@@ -2560,7 +2566,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>296</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>298</v>
       </c>
@@ -2576,7 +2582,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="214.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>300</v>
       </c>
@@ -2584,7 +2590,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="33" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>302</v>
       </c>
@@ -2592,12 +2598,20 @@
         <v>303</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="297" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>304</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>305</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/Короткие названия.xlsx
+++ b/Короткие названия.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\98rog\PycharmProjects\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\98rog\Desktop\Скуфим о Главном\Модель\Дашборд\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F83AE4-5FAF-4CC5-A9B5-471F3779CF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A6E32B-59E2-46FB-9772-760ABA493C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{C75C0F7F-FE97-4E9D-8E7A-FB1708BCE888}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
   <si>
     <t>Итоги 2024 года</t>
   </si>
@@ -969,6 +969,36 @@
   </si>
   <si>
     <t>Медведь s05</t>
+  </si>
+  <si>
+    <t>«Легенда о Vox Machine»: каким получился 4 сезон анимационного фэнтезийного сериала?</t>
+  </si>
+  <si>
+    <t>Star Fox: возвращение легендарного рельсового шутера на Nintendo Switch 2</t>
+  </si>
+  <si>
+    <t>«Властелины Вселенной»: летнее космофэнтези в духе 80-х</t>
+  </si>
+  <si>
+    <t>«Я найду тебя»: обсуждаем лучший сериал Netflix в этом году</t>
+  </si>
+  <si>
+    <t>Uncharted 3: ностальгия против правды - что не так с окончанием трилогии приключений Дрейка?</t>
+  </si>
+  <si>
+    <t>Vox Machina s4</t>
+  </si>
+  <si>
+    <t>Star Fox</t>
+  </si>
+  <si>
+    <t>Властелины Вселенной</t>
+  </si>
+  <si>
+    <t>Я найду тебя</t>
+  </si>
+  <si>
+    <t>Uncharted 3</t>
   </si>
 </sst>
 </file>
@@ -1367,10 +1397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7C6AF9-5F0C-4EB9-8185-62F3B09665F4}">
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.42578125" customWidth="1"/>
+    <col min="1" max="1" width="93.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2614,6 +2644,46 @@
         <v>309</v>
       </c>
     </row>
+    <row r="156" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>311</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>312</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>313</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>314</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
